--- a/utils/monday_sprint_sprint_2025-10.xlsx
+++ b/utils/monday_sprint_sprint_2025-10.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="921" uniqueCount="188">
   <si>
     <t>Ticket</t>
   </si>
@@ -133,6 +133,9 @@
   </si>
   <si>
     <t>10/02/2025</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
   </si>
   <si>
     <t>Semana 2</t>
@@ -1302,21 +1305,21 @@
         <v>39</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>20</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -1328,10 +1331,10 @@
         <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>19</v>
@@ -1360,7 +1363,7 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
@@ -1372,10 +1375,10 @@
         <v>17</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>36</v>
@@ -1404,7 +1407,7 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -1416,10 +1419,10 @@
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>19</v>
@@ -1448,7 +1451,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -1460,10 +1463,10 @@
         <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>19</v>
@@ -1492,7 +1495,7 @@
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>15</v>
@@ -1504,10 +1507,10 @@
         <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>19</v>
@@ -1536,7 +1539,7 @@
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
@@ -1548,10 +1551,10 @@
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>19</v>
@@ -1580,7 +1583,7 @@
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>15</v>
@@ -1592,10 +1595,10 @@
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>19</v>
@@ -1624,7 +1627,7 @@
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -1636,10 +1639,10 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>19</v>
@@ -1668,7 +1671,7 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -1680,10 +1683,10 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>19</v>
@@ -1712,7 +1715,7 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -1724,10 +1727,10 @@
         <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>19</v>
@@ -1756,7 +1759,7 @@
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
@@ -1768,10 +1771,10 @@
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>36</v>
@@ -1789,7 +1792,7 @@
         <v>17</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>21</v>
@@ -1800,7 +1803,7 @@
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -1812,10 +1815,10 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>19</v>
@@ -1844,7 +1847,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -1856,10 +1859,10 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -1877,7 +1880,7 @@
         <v>17</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="M20" s="2" t="s">
         <v>21</v>
@@ -1888,7 +1891,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -1900,10 +1903,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>36</v>
@@ -1932,7 +1935,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -1944,10 +1947,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -1976,7 +1979,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -1988,10 +1991,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -2020,7 +2023,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2032,39 +2035,39 @@
         <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2076,10 +2079,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2108,7 +2111,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2120,10 +2123,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2141,7 +2144,7 @@
         <v>17</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M26" s="2" t="s">
         <v>21</v>
@@ -2152,7 +2155,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2164,10 +2167,10 @@
         <v>17</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>19</v>
@@ -2188,7 +2191,7 @@
         <v>20</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>17</v>
@@ -2196,7 +2199,7 @@
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2208,10 +2211,10 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>19</v>
@@ -2240,7 +2243,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2252,10 +2255,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2273,7 +2276,7 @@
         <v>17</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M29" s="2" t="s">
         <v>21</v>
@@ -2284,7 +2287,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2296,10 +2299,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2328,7 +2331,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2340,10 +2343,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2361,7 +2364,7 @@
         <v>17</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>21</v>
@@ -2372,7 +2375,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2384,22 +2387,22 @@
         <v>33</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="G32" s="2" t="s">
         <v>36</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>17</v>
@@ -2408,15 +2411,15 @@
         <v>20</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2428,10 +2431,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2449,7 +2452,7 @@
         <v>17</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M33" s="2" t="s">
         <v>21</v>
@@ -2460,7 +2463,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2472,10 +2475,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2504,7 +2507,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2516,10 +2519,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2540,7 +2543,7 @@
         <v>20</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>17</v>
@@ -2548,7 +2551,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -2560,10 +2563,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2581,7 +2584,7 @@
         <v>17</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M36" s="2" t="s">
         <v>21</v>
@@ -2592,7 +2595,7 @@
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -2604,10 +2607,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -2636,7 +2639,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2648,10 +2651,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2680,7 +2683,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2692,10 +2695,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2724,7 +2727,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2736,10 +2739,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -2768,7 +2771,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2780,10 +2783,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -2804,7 +2807,7 @@
         <v>20</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>17</v>
@@ -2812,7 +2815,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -2824,10 +2827,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>36</v>
@@ -2845,7 +2848,7 @@
         <v>17</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M42" s="2" t="s">
         <v>21</v>
@@ -2856,7 +2859,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -2868,10 +2871,10 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>36</v>
@@ -2900,7 +2903,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -2912,10 +2915,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -2933,7 +2936,7 @@
         <v>17</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M44" s="2" t="s">
         <v>21</v>
@@ -2944,7 +2947,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -2956,10 +2959,10 @@
         <v>17</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>36</v>
@@ -2980,7 +2983,7 @@
         <v>20</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N45" s="2" t="s">
         <v>17</v>
@@ -2988,7 +2991,7 @@
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3000,10 +3003,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3024,7 +3027,7 @@
         <v>20</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>17</v>
@@ -3032,7 +3035,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3044,10 +3047,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>36</v>
@@ -3065,7 +3068,7 @@
         <v>17</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M47" s="2" t="s">
         <v>21</v>
@@ -3076,7 +3079,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3088,10 +3091,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>36</v>
@@ -3109,7 +3112,7 @@
         <v>17</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M48" s="2" t="s">
         <v>21</v>
@@ -3120,7 +3123,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3132,10 +3135,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3164,7 +3167,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3176,13 +3179,13 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>17</v>
@@ -3208,7 +3211,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3220,10 +3223,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3252,7 +3255,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3264,10 +3267,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3296,7 +3299,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3308,10 +3311,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3332,7 +3335,7 @@
         <v>20</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>17</v>
@@ -3340,7 +3343,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3352,10 +3355,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3384,7 +3387,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3396,10 +3399,10 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>19</v>
@@ -3428,7 +3431,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3440,10 +3443,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3464,7 +3467,7 @@
         <v>20</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>17</v>
@@ -3472,22 +3475,22 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3505,7 +3508,7 @@
         <v>17</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="M57" s="2" t="s">
         <v>21</v>
@@ -3516,7 +3519,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3528,10 +3531,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3552,7 +3555,7 @@
         <v>20</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N58" s="2" t="s">
         <v>17</v>
@@ -3560,7 +3563,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3572,10 +3575,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3593,7 +3596,7 @@
         <v>17</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="M59" s="2" t="s">
         <v>21</v>
@@ -3604,7 +3607,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3616,10 +3619,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>36</v>
@@ -3659,23 +3662,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3683,16 +3686,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3711,7 +3714,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3724,7 +3727,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -3732,7 +3735,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3763,12 +3766,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B2">
         <v>59</v>
@@ -3792,25 +3795,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -3827,13 +3830,13 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -3865,22 +3868,22 @@
         <v>11</v>
       </c>
       <c r="J11" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="K11">
         <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N11">
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="Q11">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -3897,39 +3900,39 @@
         <v>47</v>
       </c>
       <c r="M12" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="Q12">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
       <c r="P13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="Q13">
         <v>3</v>
@@ -3937,13 +3940,13 @@
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -3951,7 +3954,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -3959,7 +3962,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -3967,7 +3970,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -3975,7 +3978,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -3986,7 +3989,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -3994,44 +3997,44 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>32</v>
+        <v>100</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>99</v>
+        <v>32</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>100</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -4106,7 +4109,7 @@
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
@@ -4115,12 +4118,12 @@
         <v>0</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>15</v>
@@ -4129,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2025-10.xlsx
+++ b/utils/monday_sprint_sprint_2025-10.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="215">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -87,7 +87,7 @@
     <t>05/05/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>14/05/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,7 +102,7 @@
     <t>Maio</t>
   </si>
   <si>
-    <t>31355</t>
+    <t>9057919816</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -114,13 +114,16 @@
     <t>02/05/2025</t>
   </si>
   <si>
-    <t>31187</t>
+    <t>07/05/2025</t>
+  </si>
+  <si>
+    <t>9067852665</t>
   </si>
   <si>
     <t>TRAVA DE INCLUSÃO DE OTF COM ALERTA DE REVISÃO EM ABERTO</t>
   </si>
   <si>
-    <t>29095</t>
+    <t>9067701312</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -129,7 +132,10 @@
     <t>Diário do bordo Ajustagem</t>
   </si>
   <si>
-    <t>31344</t>
+    <t>15/05/2025</t>
+  </si>
+  <si>
+    <t>9057947740</t>
   </si>
   <si>
     <t>Alterar cor - Indicador Qualidade</t>
@@ -138,6 +144,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
@@ -159,19 +168,22 @@
     <t>19/05/2026</t>
   </si>
   <si>
-    <t>31260</t>
+    <t>9067695500</t>
   </si>
   <si>
     <t>Quantidade de moldes apontados x sistema UPR</t>
   </si>
   <si>
-    <t>31011</t>
+    <t>9067695109</t>
   </si>
   <si>
     <t>Gestão Diário de bordo moldagem - Fast loop Carrosel e ULE</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>13/05/2025</t>
+  </si>
+  <si>
+    <t>9067925431</t>
   </si>
   <si>
     <t>Desenvolver um check-in e status da operação</t>
@@ -183,40 +195,46 @@
     <t>Elaborar controle de login automatico a partir do hub no sistema de investimento</t>
   </si>
   <si>
+    <t>9067925547</t>
+  </si>
+  <si>
     <t>Criar uma visão master para visualizar os horarios agendados</t>
   </si>
   <si>
-    <t>31373</t>
+    <t>9057897211</t>
   </si>
   <si>
     <t>Atualizar dados 2024 - IROG Usinagem</t>
   </si>
   <si>
-    <t>31313</t>
+    <t>9057984965</t>
   </si>
   <si>
     <t>Apontamento digital tablet</t>
   </si>
   <si>
-    <t>31292</t>
+    <t>9058055278</t>
   </si>
   <si>
     <t>Apontamento eletrônico corte pó de ferro</t>
   </si>
   <si>
-    <t>31445</t>
+    <t>9068606427</t>
   </si>
   <si>
     <t>Alteração do Cálculo de Razão Critica para Referência por Data de Tratamento Térmico e Depósito</t>
   </si>
   <si>
-    <t>31312</t>
+    <t>17/05/2025</t>
+  </si>
+  <si>
+    <t>9058013567</t>
   </si>
   <si>
     <t>Apontamento digital tablet II</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>9067935811</t>
   </si>
   <si>
     <t>Conversão KB18 - Importação de Objetos TRN, PRC e RPT  - Homologação</t>
@@ -225,13 +243,16 @@
     <t>Implantação</t>
   </si>
   <si>
-    <t>31301</t>
+    <t>9058042730</t>
   </si>
   <si>
     <t>Add Filtro Motivo de Parada - IROG Usinagem</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>04/05/2025</t>
+  </si>
+  <si>
+    <t>9067736538</t>
   </si>
   <si>
     <t>Integração faturamento x Benner</t>
@@ -240,10 +261,7 @@
     <t>Em Análise</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>30920</t>
+    <t>8864009815</t>
   </si>
   <si>
     <t>SEQUÊNCIAS DE PRÉ-PRODUTIVO EM ABERTO</t>
@@ -255,13 +273,16 @@
     <t>Abril</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>9067721775</t>
   </si>
   <si>
     <t>Criação de Sistema de Controle impostos e declarações</t>
   </si>
   <si>
-    <t>31272</t>
+    <t>16/05/2025</t>
+  </si>
+  <si>
+    <t>9058080143</t>
   </si>
   <si>
     <t>CONSULTA DE MODELOS CPP E CLIENTE</t>
@@ -270,6 +291,9 @@
     <t>29853</t>
   </si>
   <si>
+    <t>Logística</t>
+  </si>
+  <si>
     <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
   </si>
   <si>
@@ -285,19 +309,22 @@
     <t>Fazendo</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>9067728316</t>
   </si>
   <si>
     <t>Sistema gestão de ações</t>
   </si>
   <si>
+    <t>9067737422</t>
+  </si>
+  <si>
     <t>Atualizar retroativamente o número da proforma no Benner para documentos integrados a partir 01/01/2025 (copy)</t>
   </si>
   <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>30132</t>
+    <t>8540130861</t>
   </si>
   <si>
     <t>Dispositivo luminoso para indicar se há ou não procedimento de segurança.</t>
@@ -306,33 +333,42 @@
     <t>21/02/2025</t>
   </si>
   <si>
+    <t>19/05/2025</t>
+  </si>
+  <si>
     <t>Semana 3</t>
   </si>
   <si>
     <t>Fevereiro</t>
   </si>
   <si>
-    <t>30905</t>
+    <t>8864133348</t>
   </si>
   <si>
     <t>ACVO - REUNIÃO</t>
   </si>
   <si>
-    <t>31113</t>
+    <t>9067516188</t>
   </si>
   <si>
     <t>Implementar regra para novas contas PPR para diretoria industrial</t>
   </si>
   <si>
+    <t>11/05/2025</t>
+  </si>
+  <si>
     <t>Testes</t>
   </si>
   <si>
-    <t>31311</t>
+    <t>9058028003</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DO CABEÇALHO DO AP119 E TELA TANCR011</t>
   </si>
   <si>
+    <t>9067737129</t>
+  </si>
+  <si>
     <t>Enviar PROFORMA para o Benner ao enviar NF e parcelas. Informação será usada para o controle e baixa de adiantamentos (copy)</t>
   </si>
   <si>
@@ -345,19 +381,25 @@
     <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
   </si>
   <si>
-    <t>30019</t>
+    <t>18/05/2025</t>
+  </si>
+  <si>
+    <t>9067813957</t>
   </si>
   <si>
     <t>Peças em carteira - Ultimo fornecimento +4 anos</t>
   </si>
   <si>
-    <t>31423</t>
+    <t>9058148646</t>
   </si>
   <si>
     <t>Endereço Pré-lista, do ERP para os WMS</t>
   </si>
   <si>
-    <t>31148</t>
+    <t>06/05/2025</t>
+  </si>
+  <si>
+    <t>8956038040</t>
   </si>
   <si>
     <t>NOVO FLUXO 112</t>
@@ -366,55 +408,61 @@
     <t>17/04/2025</t>
   </si>
   <si>
+    <t>9067737329</t>
+  </si>
+  <si>
     <t>Ao emitir a NF de exportação, dividir as parcelas conforme cadastro da proforma (CPC355A % parcelas ) ao invés de seguir a OTF</t>
   </si>
   <si>
-    <t>31057</t>
+    <t>9067827068</t>
   </si>
   <si>
     <t>Aplicação irog</t>
   </si>
   <si>
-    <t>31257</t>
+    <t>9058111656</t>
   </si>
   <si>
     <t>Máquina de Ensaios (ANALISE DA INTEGRAÇÃO)</t>
   </si>
   <si>
-    <t>30476</t>
+    <t>9067813872</t>
   </si>
   <si>
     <t>Grupo de Etapa LS Carrier</t>
   </si>
   <si>
-    <t>31185</t>
+    <t>9067694858</t>
   </si>
   <si>
     <t>Apontamento de refugo moldagem USE</t>
   </si>
   <si>
-    <t>31083</t>
+    <t>8956520766</t>
   </si>
   <si>
     <t>ATUALIZAÇÃO DO FLUXO 108</t>
   </si>
   <si>
-    <t>30238</t>
+    <t>9067612995</t>
   </si>
   <si>
     <t>QVD - Faturamento (Contas a receber) Validação</t>
   </si>
   <si>
-    <t>31179</t>
+    <t>9067826789</t>
   </si>
   <si>
     <t>Criação de Trava para Datas de Tratamento Térmico</t>
   </si>
   <si>
+    <t>9067737223</t>
+  </si>
+  <si>
     <t>Enviar cotação da moeda para o Benner ao faturar e integrar a NF. A partir dessa informação a variação cambial será gerada e controlada automaticamente pelo Benner (verificar layout de integração já usado no passado) (copy)</t>
   </si>
   <si>
-    <t>30406</t>
+    <t>8976556630</t>
   </si>
   <si>
     <t>Setor 596 - Reunião</t>
@@ -432,7 +480,7 @@
     <t>Revisão aplicação TOTO</t>
   </si>
   <si>
-    <t>25418</t>
+    <t>8875268812</t>
   </si>
   <si>
     <t>Melhoria no sistema de Liberação de ensaios e Ensaios destrutivos</t>
@@ -441,19 +489,19 @@
     <t>07/04/2025</t>
   </si>
   <si>
-    <t>26568</t>
+    <t>8875302466</t>
   </si>
   <si>
     <t>Certificado da qualidade só aparecer ensaios aprovados</t>
   </si>
   <si>
-    <t>28708</t>
+    <t>9067571055</t>
   </si>
   <si>
     <t>Bloco K Reroativo 2019/01 a 2023/09</t>
   </si>
   <si>
-    <t>31167</t>
+    <t>9067603885</t>
   </si>
   <si>
     <t>Página para Conta Insertos</t>
@@ -462,49 +510,46 @@
     <t>Baixa</t>
   </si>
   <si>
-    <t>31388</t>
+    <t>9057839843</t>
   </si>
   <si>
     <t>Bloqueio por operação no apontamento eletrônico</t>
   </si>
   <si>
-    <t>31399</t>
+    <t>9057783592</t>
   </si>
   <si>
     <t>OTFs CANCELADAS - CAMPO "TIPO DE OTF"</t>
   </si>
   <si>
-    <t>31556</t>
+    <t>9137613635</t>
   </si>
   <si>
     <t>GRUPOS DE RECURSO - MÁQUINAS DE USINAGEM</t>
   </si>
   <si>
-    <t>13/05/2025</t>
-  </si>
-  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>31376</t>
+    <t>9057860147</t>
   </si>
   <si>
     <t>Integração de Sistema Logística x Databook</t>
   </si>
   <si>
-    <t>31378</t>
+    <t>9057851254</t>
   </si>
   <si>
     <t>CONSULTA ALERTAS E PENDÊNCIAS</t>
   </si>
   <si>
-    <t>25807</t>
+    <t>8976606092</t>
   </si>
   <si>
     <t>Reunião - Homologação Faseamento de Vendas</t>
   </si>
   <si>
-    <t>28659</t>
+    <t>9073040536</t>
   </si>
   <si>
     <t>Análise</t>
@@ -513,37 +558,34 @@
     <t>Tabela Lead Time</t>
   </si>
   <si>
-    <t>31259</t>
+    <t>8982362862</t>
   </si>
   <si>
     <t>Tela para apontamento de parada FL</t>
   </si>
   <si>
-    <t>31022</t>
+    <t>9081754389</t>
   </si>
   <si>
     <t>QlikSense Controle de Investimentos Dashboard</t>
   </si>
   <si>
-    <t>06/05/2025</t>
-  </si>
-  <si>
-    <t>31189</t>
+    <t>12/05/2025</t>
+  </si>
+  <si>
+    <t>9093391495</t>
   </si>
   <si>
     <t>Diferença CRP x BI</t>
   </si>
   <si>
-    <t>07/05/2025</t>
-  </si>
-  <si>
     <t>Dashboard de Change Log - Governança de TI</t>
   </si>
   <si>
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-10</t>
+    <t>Fev/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -1176,7 +1218,7 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1193,7 +1235,7 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
@@ -1205,10 +1247,10 @@
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1223,7 +1265,7 @@
         <v>23</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1240,22 +1282,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1270,7 +1312,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1287,7 +1329,7 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>16</v>
@@ -1299,10 +1341,10 @@
         <v>18</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -1317,7 +1359,7 @@
         <v>32</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
@@ -1334,37 +1376,37 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1381,7 +1423,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
@@ -1393,10 +1435,10 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1411,7 +1453,7 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L8" s="2" t="s">
         <v>25</v>
@@ -1428,25 +1470,25 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>21</v>
@@ -1458,7 +1500,7 @@
         <v>23</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
@@ -1475,7 +1517,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
@@ -1487,10 +1529,10 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1505,7 +1547,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1522,7 +1564,7 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
@@ -1534,10 +1576,10 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1569,7 +1611,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1581,10 +1623,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1599,7 +1641,7 @@
         <v>23</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>25</v>
@@ -1616,7 +1658,7 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
@@ -1628,10 +1670,10 @@
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1646,7 +1688,7 @@
         <v>32</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1663,7 +1705,7 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
@@ -1675,10 +1717,10 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1710,7 +1752,7 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
@@ -1722,10 +1764,10 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1740,7 +1782,7 @@
         <v>32</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L15" s="2" t="s">
         <v>25</v>
@@ -1757,22 +1799,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1787,7 +1829,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1804,7 +1846,7 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
@@ -1816,10 +1858,10 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
@@ -1851,25 +1893,25 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>67</v>
+        <v>73</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>68</v>
+        <v>74</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>21</v>
@@ -1881,10 +1923,10 @@
         <v>23</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="M18" s="2" t="s">
         <v>26</v>
@@ -1898,7 +1940,7 @@
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>16</v>
@@ -1910,10 +1952,10 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
@@ -1928,7 +1970,7 @@
         <v>32</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
@@ -1945,7 +1987,7 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
@@ -1957,10 +1999,10 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -1975,13 +2017,13 @@
         <v>23</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
         <v>27</v>
@@ -1992,7 +2034,7 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
@@ -2004,13 +2046,13 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>21</v>
@@ -2019,10 +2061,10 @@
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L21" s="2" t="s">
         <v>25</v>
@@ -2034,27 +2076,27 @@
         <v>27</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2069,7 +2111,7 @@
         <v>23</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>88</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2086,7 +2128,7 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
@@ -2098,10 +2140,10 @@
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2116,7 +2158,7 @@
         <v>32</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2133,43 +2175,43 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>30</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>27</v>
@@ -2180,7 +2222,7 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
@@ -2192,10 +2234,10 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2210,7 +2252,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2227,7 +2269,7 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>72</v>
+        <v>100</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
@@ -2239,10 +2281,10 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>92</v>
+        <v>101</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2257,13 +2299,13 @@
         <v>23</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>27</v>
@@ -2274,7 +2316,7 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>94</v>
+        <v>103</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>16</v>
@@ -2286,10 +2328,10 @@
         <v>18</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>95</v>
+        <v>104</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
@@ -2301,10 +2343,10 @@
         <v>22</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>96</v>
+        <v>105</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L27" s="2" t="s">
         <v>25</v>
@@ -2313,15 +2355,15 @@
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O27" s="2" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>99</v>
+        <v>109</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
@@ -2333,10 +2375,10 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
@@ -2348,10 +2390,10 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
@@ -2363,12 +2405,12 @@
         <v>27</v>
       </c>
       <c r="O28" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>101</v>
+        <v>111</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
@@ -2380,10 +2422,10 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2398,13 +2440,13 @@
         <v>23</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
@@ -2415,7 +2457,7 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>104</v>
+        <v>115</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
@@ -2427,10 +2469,10 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2445,7 +2487,7 @@
         <v>32</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2462,7 +2504,7 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>72</v>
+        <v>117</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
@@ -2474,10 +2516,10 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2492,13 +2534,13 @@
         <v>23</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>27</v>
@@ -2509,37 +2551,37 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>107</v>
+        <v>119</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>108</v>
+        <v>120</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>109</v>
+        <v>121</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>87</v>
+        <v>95</v>
       </c>
       <c r="I32" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2556,7 +2598,7 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
@@ -2568,10 +2610,10 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2586,13 +2628,13 @@
         <v>23</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>27</v>
@@ -2603,7 +2645,7 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
@@ -2615,10 +2657,10 @@
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>113</v>
+        <v>126</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2633,7 +2675,7 @@
         <v>32</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>127</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2650,7 +2692,7 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>114</v>
+        <v>128</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
@@ -2662,10 +2704,10 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2677,10 +2719,10 @@
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L35" s="2" t="s">
         <v>25</v>
@@ -2689,15 +2731,15 @@
         <v>26</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O35" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>72</v>
+        <v>131</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2709,10 +2751,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>117</v>
+        <v>132</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2727,13 +2769,13 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L36" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N36" s="2" t="s">
         <v>27</v>
@@ -2744,7 +2786,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>118</v>
+        <v>133</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2756,10 +2798,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>119</v>
+        <v>134</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2774,7 +2816,7 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L37" s="2" t="s">
         <v>25</v>
@@ -2791,7 +2833,7 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>120</v>
+        <v>135</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
@@ -2803,10 +2845,10 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>121</v>
+        <v>136</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -2838,7 +2880,7 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
@@ -2850,10 +2892,10 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -2868,7 +2910,7 @@
         <v>23</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -2885,7 +2927,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>124</v>
+        <v>139</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
@@ -2897,10 +2939,10 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>125</v>
+        <v>140</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -2915,7 +2957,7 @@
         <v>23</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -2932,7 +2974,7 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>126</v>
+        <v>141</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
@@ -2944,10 +2986,10 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>127</v>
+        <v>142</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -2959,10 +3001,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -2971,15 +3013,15 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O41" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>128</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
@@ -2991,13 +3033,13 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>129</v>
+        <v>144</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>21</v>
@@ -3009,13 +3051,13 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>122</v>
       </c>
       <c r="L42" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>27</v>
@@ -3026,7 +3068,7 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>130</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
@@ -3038,13 +3080,13 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>131</v>
+        <v>146</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
@@ -3056,7 +3098,7 @@
         <v>23</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3073,7 +3115,7 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>72</v>
+        <v>147</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
@@ -3085,10 +3127,10 @@
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3103,13 +3145,13 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L44" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N44" s="2" t="s">
         <v>27</v>
@@ -3120,7 +3162,7 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>16</v>
@@ -3132,13 +3174,13 @@
         <v>18</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>21</v>
@@ -3147,10 +3189,10 @@
         <v>22</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>106</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
@@ -3159,30 +3201,30 @@
         <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="O45" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>20</v>
@@ -3194,10 +3236,10 @@
         <v>22</v>
       </c>
       <c r="J46" s="2" t="s">
-        <v>116</v>
+        <v>130</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
@@ -3206,15 +3248,15 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="O46" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3226,13 +3268,13 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>21</v>
@@ -3241,27 +3283,27 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L47" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O47" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
@@ -3273,13 +3315,13 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>21</v>
@@ -3288,27 +3330,27 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L48" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O48" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
@@ -3320,10 +3362,10 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3338,7 +3380,7 @@
         <v>23</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3355,7 +3397,7 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
@@ -3367,13 +3409,13 @@
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>21</v>
@@ -3385,7 +3427,7 @@
         <v>23</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3402,7 +3444,7 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
@@ -3414,10 +3456,10 @@
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3432,7 +3474,7 @@
         <v>32</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3449,7 +3491,7 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
@@ -3461,10 +3503,10 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3479,7 +3521,7 @@
         <v>32</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3496,7 +3538,7 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
@@ -3508,10 +3550,10 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3523,10 +3565,10 @@
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>155</v>
+        <v>55</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3535,7 +3577,7 @@
         <v>26</v>
       </c>
       <c r="N53" s="2" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="O53" s="2" t="s">
         <v>28</v>
@@ -3543,7 +3585,7 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
@@ -3555,10 +3597,10 @@
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3573,7 +3615,7 @@
         <v>32</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
@@ -3590,7 +3632,7 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
@@ -3602,10 +3644,10 @@
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="G55" s="2" t="s">
         <v>20</v>
@@ -3620,7 +3662,7 @@
         <v>32</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>70</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
@@ -3637,7 +3679,7 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
@@ -3649,10 +3691,10 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3664,7 +3706,7 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>24</v>
@@ -3676,30 +3718,30 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="O56" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3714,13 +3756,13 @@
         <v>23</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>78</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
         <v>27</v>
@@ -3731,7 +3773,7 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
@@ -3743,10 +3785,10 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>20</v>
@@ -3758,10 +3800,10 @@
         <v>22</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>24</v>
+        <v>39</v>
       </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
@@ -3770,30 +3812,30 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="O58" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3805,16 +3847,16 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>170</v>
+        <v>127</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>185</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>75</v>
+        <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
         <v>27</v>
@@ -3825,7 +3867,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
@@ -3837,13 +3879,13 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>21</v>
@@ -3852,7 +3894,7 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>173</v>
+        <v>33</v>
       </c>
       <c r="K60" s="2" t="s">
         <v>24</v>
@@ -3883,23 +3925,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>174</v>
+        <v>188</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="B2" t="s">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="D2" t="s">
-        <v>177</v>
+        <v>191</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>192</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -3907,16 +3949,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>180</v>
+        <v>194</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>181</v>
+        <v>195</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>182</v>
+        <v>196</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -3927,15 +3969,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>380</v>
+        <v>23.02</v>
       </c>
       <c r="J5" s="4">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>183</v>
+        <v>197</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -3948,7 +3990,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="K23">
         <v>1</v>
@@ -3956,7 +3998,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>184</v>
+        <v>198</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -3987,12 +4029,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>185</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>179</v>
+        <v>193</v>
       </c>
       <c r="B2">
         <v>59</v>
@@ -4006,35 +4048,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>380</v>
+        <v>23.02</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>186</v>
+        <v>200</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>187</v>
+        <v>201</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>188</v>
+        <v>202</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -4042,7 +4084,7 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="D10" t="s">
         <v>30</v>
@@ -4051,13 +4093,13 @@
         <v>47</v>
       </c>
       <c r="G10" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -4072,18 +4114,24 @@
         <v>27</v>
       </c>
       <c r="Q10">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>92</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="D11" t="s">
         <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="4:17" x14ac:dyDescent="0.25">
-      <c r="D11" t="s">
-        <v>36</v>
       </c>
       <c r="E11">
         <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="H11">
         <v>11</v>
@@ -4092,22 +4140,28 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>46</v>
+        <v>59</v>
       </c>
       <c r="M11" t="s">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="N11">
         <v>8</v>
       </c>
       <c r="P11" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="Q11">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>43</v>
+      </c>
+      <c r="B12">
         <v>1</v>
       </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
         <v>17</v>
       </c>
@@ -4121,59 +4175,53 @@
         <v>47</v>
       </c>
       <c r="J12" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="K12">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="N12">
         <v>0</v>
       </c>
       <c r="P12" t="s">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="Q12">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="4:14" x14ac:dyDescent="0.25">
       <c r="D13" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="H13">
         <v>1</v>
       </c>
       <c r="M13" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
-      <c r="P13" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
     </row>
     <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="N14">
         <v>1</v>
@@ -4181,7 +4229,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="N15">
         <v>0</v>
@@ -4189,7 +4237,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -4197,7 +4245,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>74</v>
+        <v>81</v>
       </c>
       <c r="N17">
         <v>1</v>
@@ -4205,10 +4253,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -4216,7 +4264,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -4224,142 +4272,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>40</v>
+        <v>79</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>365</v>
+        <v>467</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>42</v>
+        <v>80</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>16</v>
+        <v>92</v>
       </c>
       <c r="F22" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>19</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>29</v>
+        <v>100</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>31</v>
+        <v>101</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>33</v>
+        <v>111</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>112</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>35</v>
+        <v>117</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>37</v>
+        <v>118</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>38</v>
+        <v>123</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>39</v>
+        <v>124</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>48</v>
+        <v>131</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>49</v>
+        <v>132</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>50</v>
+        <v>143</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>51</v>
+        <v>144</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>52</v>
+        <v>147</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>148</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>54</v>
+        <v>155</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>467</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>55</v>
+        <v>156</v>
       </c>
     </row>
   </sheetData>
